--- a/testakten/sozialrecht-elektrorollstuhl-koerner-oldenburg/xlsx/verfahrenskalender_und_kostenvergleich.xlsx
+++ b/testakten/sozialrecht-elektrorollstuhl-koerner-oldenburg/xlsx/verfahrenskalender_und_kostenvergleich.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Zustaendig</t>
+          <t>Zuständig</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,6 @@
           <t>Antrag Elektrorollstuhl gestellt</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Kläger</t>
@@ -477,10 +476,9 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aerztliche Verordnung Dr. Stahlmann</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Ärztliche Verordnung Dr. Stahlmann</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Hausarzt</t>
@@ -498,7 +496,6 @@
           <t>Facharztbericht Dr. Radtke</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Facharzt</t>
@@ -516,10 +513,9 @@
           <t>Kostenvoranschlag RehaTechnik Albrecht</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sanitaetshaus</t>
+          <t>Sanitätshaus</t>
         </is>
       </c>
     </row>
@@ -534,7 +530,6 @@
           <t>MD-Stellungnahme Ablehnungsempfehlung</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Medizinischer Dienst</t>
@@ -552,7 +547,6 @@
           <t>Ablehnungsbescheid</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>Kasse</t>
@@ -570,7 +564,6 @@
           <t>Privates Reha-Gutachten</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>RehaKompetenz Nordwest</t>
@@ -610,7 +603,6 @@
           <t>Widerspruchsbescheid</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>Kasse</t>
@@ -650,7 +642,6 @@
           <t>Mandatierung Kanzlei Brammertz</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Kläger</t>
@@ -668,7 +659,6 @@
           <t>Klageschrift gefertigt</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Kanzlei</t>
@@ -708,7 +698,6 @@
           <t>Klageerwiderung Kasse</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>Kasse</t>
@@ -726,7 +715,6 @@
           <t>Beweisbeschluss Sozialgericht</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>Sozialgericht Oldenburg</t>
@@ -741,10 +729,9 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Untersuchungstermin Sachverstaendige</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>Untersuchungstermin Sachverständige</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Prof. Dr. Wickenrath</t>
@@ -762,7 +749,6 @@
           <t>Gutachten vorgelegt</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>Prof. Dr. Wickenrath</t>
@@ -777,10 +763,9 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Terminsverfuegung</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Terminsverfügung</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Sozialgericht Oldenburg</t>
@@ -795,7 +780,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Muendliche Verhandlung</t>
+          <t>Mündliche Verhandlung</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -842,7 +827,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Foerderfaehig</t>
+          <t>Förderfähig</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -854,7 +839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unterarmgehstuetze</t>
+          <t>Unterarmgehstütze</t>
         </is>
       </c>
       <c r="B2" t="n">
